--- a/Kamplogg FCSP.xlsx
+++ b/Kamplogg FCSP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30502"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjorn\Desktop\Privat\Partisan Lillestrøm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5FACD5D-8BEA-4757-BA2F-6C2596D4E4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="489" documentId="13_ncr:1_{13C26D5C-C8A7-4B63-813B-201D061E3392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F9A35BD-4D01-4B3C-912B-B4C581292E1D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="67">
   <si>
     <t>Kamplogg  - Partisan Lillestrøm</t>
   </si>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I2" s="38">
         <f>SUM(I3:I5)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J2" s="39">
         <f>I2/$I$2</f>
@@ -1223,11 +1223,11 @@
       </c>
       <c r="I3" s="13">
         <f>SUMIF(F3:F360,"Seier",A3:A360)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" s="16">
         <f>I3/$I$2</f>
-        <v>0.46153846153846156</v>
+        <v>0.47169811320754718</v>
       </c>
       <c r="K3" s="45"/>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="J4" s="18">
         <f t="shared" ref="J3:J5" si="0">I4/$I$2</f>
-        <v>0.25</v>
+        <v>0.24528301886792453</v>
       </c>
       <c r="K4" s="45"/>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="J5" s="21">
         <f t="shared" si="0"/>
-        <v>0.28846153846153844</v>
+        <v>0.28301886792452829</v>
       </c>
       <c r="K5" s="45"/>
     </row>
@@ -2526,11 +2526,21 @@
       <c r="A55" s="36">
         <v>1</v>
       </c>
-      <c r="B55" s="24"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="10"/>
+      <c r="B55" s="24">
+        <v>46277</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E55" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="56" spans="1:11" s="44" customFormat="1">
       <c r="A56" s="36">

--- a/Kamplogg FCSP.xlsx
+++ b/Kamplogg FCSP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30516"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjorn\Desktop\Privat\Partisan Lillestrøm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="489" documentId="13_ncr:1_{13C26D5C-C8A7-4B63-813B-201D061E3392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F9A35BD-4D01-4B3C-912B-B4C581292E1D}"/>
+  <xr:revisionPtr revIDLastSave="508" documentId="13_ncr:1_{13C26D5C-C8A7-4B63-813B-201D061E3392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2197C71D-A8DE-4514-8099-786F5AAA72FD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="69">
   <si>
     <t>Kamplogg  - Partisan Lillestrøm</t>
   </si>
@@ -198,6 +198,12 @@
   </si>
   <si>
     <t>Arminia Bielefeld</t>
+  </si>
+  <si>
+    <t>FC St. Pauli U15</t>
+  </si>
+  <si>
+    <t>Niendorfer TSV</t>
   </si>
   <si>
     <t>SV Werder Bremen</t>
@@ -1136,10 +1142,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y80"/>
+  <dimension ref="A1:Y81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.5" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" customWidth="1"/>
     <col min="2" max="2" width="10.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.75" bestFit="1" customWidth="1"/>
@@ -1190,7 +1196,7 @@
       </c>
       <c r="I2" s="38">
         <f>SUM(I3:I5)</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J2" s="39">
         <f>I2/$I$2</f>
@@ -1222,12 +1228,12 @@
         <v>11</v>
       </c>
       <c r="I3" s="13">
-        <f>SUMIF(F3:F360,"Seier",A3:A360)</f>
-        <v>25</v>
+        <f>SUMIF(F3:F361,"Seier",A3:A361)</f>
+        <v>26</v>
       </c>
       <c r="J3" s="16">
         <f>I3/$I$2</f>
-        <v>0.47169811320754718</v>
+        <v>0.48148148148148145</v>
       </c>
       <c r="K3" s="45"/>
     </row>
@@ -1255,12 +1261,12 @@
         <v>14</v>
       </c>
       <c r="I4" s="14">
-        <f>SUMIF(F3:F360,"Uavgjort",A3:A360)</f>
+        <f>SUMIF(F3:F361,"Uavgjort",A3:A361)</f>
         <v>13</v>
       </c>
       <c r="J4" s="18">
         <f t="shared" ref="J3:J5" si="0">I4/$I$2</f>
-        <v>0.24528301886792453</v>
+        <v>0.24074074074074073</v>
       </c>
       <c r="K4" s="45"/>
     </row>
@@ -1288,12 +1294,12 @@
         <v>17</v>
       </c>
       <c r="I5" s="20">
-        <f>SUMIF(F3:F360,"Tap",A3:A360)</f>
+        <f>SUMIF(F3:F361,"Tap",A3:A361)</f>
         <v>15</v>
       </c>
       <c r="J5" s="21">
         <f t="shared" si="0"/>
-        <v>0.28301886792452829</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="K5" s="45"/>
     </row>
@@ -1926,20 +1932,20 @@
       <c r="A31" s="36">
         <v>1</v>
       </c>
-      <c r="B31" s="31">
-        <v>44499</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="B31" s="24">
+        <v>44443</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="32" t="s">
-        <v>19</v>
+      <c r="D31" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>26</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G31" s="44"/>
       <c r="H31" s="44"/>
@@ -1951,20 +1957,20 @@
       <c r="A32" s="36">
         <v>1</v>
       </c>
-      <c r="B32" s="24">
-        <v>44638</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E32" s="34" t="s">
-        <v>34</v>
+      <c r="B32" s="31">
+        <v>44499</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="32" t="s">
+        <v>19</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G32" s="44"/>
       <c r="H32" s="44"/>
@@ -1977,16 +1983,16 @@
         <v>1</v>
       </c>
       <c r="B33" s="24">
-        <v>44758</v>
+        <v>44638</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E33" s="30" t="s">
-        <v>36</v>
+        <v>57</v>
+      </c>
+      <c r="E33" s="34" t="s">
+        <v>34</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>11</v>
@@ -2001,20 +2007,20 @@
       <c r="A34" s="36">
         <v>1</v>
       </c>
-      <c r="B34" s="40">
-        <v>44856</v>
-      </c>
-      <c r="C34" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="43" t="s">
-        <v>16</v>
+      <c r="B34" s="24">
+        <v>44758</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G34" s="44"/>
       <c r="H34" s="44"/>
@@ -2026,20 +2032,20 @@
       <c r="A35" s="36">
         <v>1</v>
       </c>
-      <c r="B35" s="24">
-        <v>44863</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" s="30" t="s">
-        <v>19</v>
+      <c r="B35" s="40">
+        <v>44856</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>16</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G35" s="44"/>
       <c r="H35" s="44"/>
@@ -2052,19 +2058,19 @@
         <v>1</v>
       </c>
       <c r="B36" s="24">
-        <v>44962</v>
+        <v>44863</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E36" s="30" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G36" s="44"/>
       <c r="H36" s="44"/>
@@ -2077,16 +2083,16 @@
         <v>1</v>
       </c>
       <c r="B37" s="24">
-        <v>44996</v>
+        <v>44962</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>11</v>
@@ -2102,19 +2108,19 @@
         <v>1</v>
       </c>
       <c r="B38" s="24">
-        <v>45074</v>
+        <v>44996</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="E38" s="30" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G38" s="44"/>
       <c r="H38" s="44"/>
@@ -2127,16 +2133,16 @@
         <v>1</v>
       </c>
       <c r="B39" s="24">
-        <v>45143</v>
+        <v>45074</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E39" s="30" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>20</v>
@@ -2151,20 +2157,20 @@
       <c r="A40" s="36">
         <v>1</v>
       </c>
-      <c r="B40" s="40">
-        <v>45199</v>
-      </c>
-      <c r="C40" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="D40" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="43" t="s">
-        <v>32</v>
+      <c r="B40" s="24">
+        <v>45143</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" s="30" t="s">
+        <v>45</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G40" s="44"/>
       <c r="H40" s="44"/>
@@ -2176,17 +2182,17 @@
       <c r="A41" s="36">
         <v>1</v>
       </c>
-      <c r="B41" s="24">
-        <v>45408</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="30" t="s">
-        <v>34</v>
+      <c r="B41" s="40">
+        <v>45199</v>
+      </c>
+      <c r="C41" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="D41" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="43" t="s">
+        <v>32</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>11</v>
@@ -2201,20 +2207,20 @@
       <c r="A42" s="36">
         <v>1</v>
       </c>
-      <c r="B42" s="40">
-        <v>45415</v>
-      </c>
-      <c r="C42" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="D42" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="43" t="s">
+      <c r="B42" s="24">
+        <v>45408</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="30" t="s">
         <v>34</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G42" s="44"/>
       <c r="H42" s="44"/>
@@ -2226,17 +2232,17 @@
       <c r="A43" s="36">
         <v>1</v>
       </c>
-      <c r="B43" s="24">
-        <v>45529</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E43" s="34" t="s">
-        <v>39</v>
+      <c r="B43" s="40">
+        <v>45415</v>
+      </c>
+      <c r="C43" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="43" t="s">
+        <v>34</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>17</v>
@@ -2252,19 +2258,19 @@
         <v>1</v>
       </c>
       <c r="B44" s="24">
-        <v>45591</v>
+        <v>45529</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E44" s="34" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G44" s="44"/>
       <c r="H44" s="44"/>
@@ -2277,19 +2283,19 @@
         <v>1</v>
       </c>
       <c r="B45" s="24">
-        <v>45625</v>
+        <v>45591</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E45" s="30" t="s">
-        <v>28</v>
+        <v>61</v>
+      </c>
+      <c r="E45" s="34" t="s">
+        <v>45</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G45" s="44"/>
       <c r="H45" s="44"/>
@@ -2302,19 +2308,19 @@
         <v>1</v>
       </c>
       <c r="B46" s="24">
-        <v>45780</v>
+        <v>45625</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E46" s="34" t="s">
-        <v>52</v>
+        <v>62</v>
+      </c>
+      <c r="E46" s="30" t="s">
+        <v>28</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G46" s="44"/>
       <c r="H46" s="44"/>
@@ -2327,19 +2333,19 @@
         <v>1</v>
       </c>
       <c r="B47" s="24">
-        <v>45892</v>
+        <v>45780</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E47" s="30" t="s">
         <v>63</v>
       </c>
+      <c r="E47" s="34" t="s">
+        <v>52</v>
+      </c>
       <c r="F47" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G47" s="44"/>
       <c r="H47" s="44"/>
@@ -2352,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="B48" s="24">
-        <v>45962</v>
+        <v>45892</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>8</v>
@@ -2360,11 +2366,11 @@
       <c r="D48" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E48" s="34" t="s">
-        <v>51</v>
+      <c r="E48" s="30" t="s">
+        <v>65</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G48" s="44"/>
       <c r="H48" s="44"/>
@@ -2377,16 +2383,16 @@
         <v>1</v>
       </c>
       <c r="B49" s="24">
-        <v>45984</v>
+        <v>45962</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="E49" s="34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>17</v>
@@ -2401,19 +2407,19 @@
       <c r="A50" s="36">
         <v>1</v>
       </c>
-      <c r="B50" s="40">
-        <v>45990</v>
-      </c>
-      <c r="C50" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="F50" s="47" t="s">
+      <c r="B50" s="24">
+        <v>45984</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="F50" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G50" s="44"/>
@@ -2426,20 +2432,20 @@
       <c r="A51" s="36">
         <v>1</v>
       </c>
-      <c r="B51" s="24">
-        <v>46004</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E51" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>11</v>
+      <c r="B51" s="40">
+        <v>45990</v>
+      </c>
+      <c r="C51" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="F51" s="47" t="s">
+        <v>17</v>
       </c>
       <c r="G51" s="44"/>
       <c r="H51" s="44"/>
@@ -2452,19 +2458,19 @@
         <v>1</v>
       </c>
       <c r="B52" s="24">
-        <v>46129</v>
+        <v>46004</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E52" s="48" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G52" s="44"/>
       <c r="H52" s="44"/>
@@ -2477,13 +2483,13 @@
         <v>1</v>
       </c>
       <c r="B53" s="24">
-        <v>46243</v>
+        <v>46129</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="E53" s="48" t="s">
         <v>19</v>
@@ -2502,19 +2508,19 @@
         <v>1</v>
       </c>
       <c r="B54" s="24">
-        <v>46264</v>
+        <v>46243</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E54" s="48" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G54" s="44"/>
       <c r="H54" s="44"/>
@@ -2522,35 +2528,50 @@
       <c r="J54" s="44"/>
       <c r="K54" s="44"/>
     </row>
-    <row r="55" spans="1:11" s="44" customFormat="1">
+    <row r="55" spans="1:11">
       <c r="A55" s="36">
         <v>1</v>
       </c>
       <c r="B55" s="24">
-        <v>46277</v>
+        <v>46264</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="E55" s="48" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>11</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="44"/>
+      <c r="J55" s="44"/>
+      <c r="K55" s="44"/>
     </row>
     <row r="56" spans="1:11" s="44" customFormat="1">
       <c r="A56" s="36">
         <v>1</v>
       </c>
-      <c r="B56" s="24"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="10"/>
+      <c r="B56" s="24">
+        <v>46277</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E56" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="57" spans="1:11" s="44" customFormat="1">
       <c r="A57" s="36">
@@ -2692,7 +2713,16 @@
       <c r="E70" s="48"/>
       <c r="F70" s="10"/>
     </row>
-    <row r="71" spans="1:6" s="44" customFormat="1"/>
+    <row r="71" spans="1:6" s="44" customFormat="1">
+      <c r="A71" s="36">
+        <v>1</v>
+      </c>
+      <c r="B71" s="24"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="10"/>
+    </row>
     <row r="72" spans="1:6" s="44" customFormat="1"/>
     <row r="73" spans="1:6" s="44" customFormat="1"/>
     <row r="74" spans="1:6" s="44" customFormat="1"/>
@@ -2702,6 +2732,7 @@
     <row r="78" spans="1:6" s="44" customFormat="1"/>
     <row r="79" spans="1:6" s="44" customFormat="1"/>
     <row r="80" spans="1:6" s="44" customFormat="1"/>
+    <row r="81" s="44" customFormat="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:E1"/>
